--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-specimen.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-specimen.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2508" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2508" uniqueCount="422">
   <si>
     <t>Property</t>
   </si>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Specimen - Fr Specimen</t>
+    <t>Specimen - Fr Prélèvement</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:49:50+00:00</t>
+    <t>2025-09-03T12:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1132,6 +1132,9 @@
   </si>
   <si>
     <t>Specimen.processing.procedure.coding.code</t>
+  </si>
+  <si>
+    <t>Acte de prélèvement</t>
   </si>
   <si>
     <t>Specimen.processing.procedure.coding.display</t>
@@ -7582,7 +7585,7 @@
         <v>105</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>294</v>
+        <v>358</v>
       </c>
       <c r="M54" t="s" s="2">
         <v>295</v>
@@ -7664,10 +7667,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7775,10 +7778,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7888,10 +7891,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8001,10 +8004,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8030,10 +8033,10 @@
         <v>174</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8084,7 +8087,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8099,21 +8102,21 @@
         <v>97</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8139,10 +8142,10 @@
         <v>229</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8193,7 +8196,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8219,10 +8222,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8248,10 +8251,10 @@
         <v>202</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8302,7 +8305,7 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8317,7 +8320,7 @@
         <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>76</v>
@@ -8328,10 +8331,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8437,10 +8440,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8548,10 +8551,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8661,10 +8664,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8690,10 +8693,10 @@
         <v>143</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8744,7 +8747,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -8765,15 +8768,15 @@
         <v>76</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8799,10 +8802,10 @@
         <v>208</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8853,7 +8856,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -8868,7 +8871,7 @@
         <v>97</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>76</v>
@@ -8879,10 +8882,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8908,10 +8911,10 @@
         <v>165</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8941,10 +8944,10 @@
         <v>248</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>76</v>
@@ -8962,7 +8965,7 @@
         <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -8983,15 +8986,15 @@
         <v>76</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9017,10 +9020,10 @@
         <v>240</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9071,7 +9074,7 @@
         <v>76</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9086,21 +9089,21 @@
         <v>97</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9126,10 +9129,10 @@
         <v>240</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9180,7 +9183,7 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9195,21 +9198,21 @@
         <v>97</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9232,13 +9235,13 @@
         <v>76</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9268,10 +9271,10 @@
         <v>248</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>76</v>
@@ -9289,7 +9292,7 @@
         <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9304,21 +9307,21 @@
         <v>97</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9344,16 +9347,16 @@
         <v>165</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>76</v>
@@ -9381,10 +9384,10 @@
         <v>330</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>76</v>
@@ -9402,7 +9405,7 @@
         <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9423,15 +9426,15 @@
         <v>76</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9454,13 +9457,13 @@
         <v>76</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L71" t="s" s="2">
         <v>50</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9511,7 +9514,7 @@
         <v>76</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -9526,13 +9529,13 @@
         <v>97</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>

--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-specimen.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
